--- a/backend/static/excel_data/962677eff8fe7619c70e350c7a754506/non_financial_batch_962677eff8fe7619c70e350c7a754506.xlsx
+++ b/backend/static/excel_data/962677eff8fe7619c70e350c7a754506/non_financial_batch_962677eff8fe7619c70e350c7a754506.xlsx
@@ -523,7 +523,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>作文评分记录</t>
+          <t>学生作文评分表</t>
         </is>
       </c>
     </row>
@@ -856,12 +856,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>续写与原文衔接自然,词汇灵活</t>
+          <t>续写与原文衔接自然，词汇灵活</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>作文评分记录</t>
+          <t>学生作文评分表</t>
         </is>
       </c>
     </row>
@@ -913,12 +913,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>细节生动,结尾有力,略有小错。</t>
+          <t>细节生动，结尾有力，略有小错。</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>作文评分记录</t>
+          <t>学生作文评分表</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>偏离原文少许,但表达尚清楚</t>
+          <t>偏离原文少许，但表达尚清楚</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>作文评分记录</t>
+          <t>学生作文评分表</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>续写与原文衔接自然,词汇灵活。</t>
+          <t>续写与原文衔接自然，词汇灵活。</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>作文评分记录</t>
+          <t>学生作文评分表</t>
         </is>
       </c>
     </row>
@@ -1084,12 +1084,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>句式较单一,字数刚好,书写可提高。</t>
+          <t>句式较单一，字数刚好，书写可提高。</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>作文评分记录</t>
+          <t>学生作文评分表</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>情节略显突兀,语言可读性较好。</t>
+          <t>情节略显突兀，语言可读性较好。</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>作文评分记录</t>
+          <t>学生作文评分表</t>
         </is>
       </c>
     </row>
@@ -1198,12 +1198,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>内容贴合原文,句式丰富,卷面清爽。</t>
+          <t>内容贴合原文，句式丰富，卷面清爽。</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>作文评分记录</t>
+          <t>学生作文评分表</t>
         </is>
       </c>
     </row>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>故事完整,结构紧凑,表达有亮点。</t>
+          <t>故事完整，结构紧凑，表达有亮点。</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>作文评分记录</t>
+          <t>学生作文评分表</t>
         </is>
       </c>
     </row>
@@ -1312,12 +1312,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>主题明确,逻辑清晰,书写再工整些更佳。</t>
+          <t>主题明确，逻辑清晰，书写再工整些更佳。</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>作文评分记录</t>
+          <t>学生作文评分表</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>续写与原文衔接自然,词汇灵活。</t>
+          <t>续写与原文衔接自然，词汇灵活。</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>作文评分记录</t>
+          <t>学生作文评分表</t>
         </is>
       </c>
     </row>
@@ -1426,12 +1426,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>内容基本相关,结构需更紧凑。</t>
+          <t>内容基本相关，结构需更紧凑。</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>作文评分记录</t>
+          <t>学生作文评分表</t>
         </is>
       </c>
     </row>
@@ -1483,12 +1483,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>情节略显突兀,语言可读性较好。</t>
+          <t>情节略显突兀，语言可读性较好。</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>作文评分记录</t>
+          <t>学生作文评分表</t>
         </is>
       </c>
     </row>
@@ -1540,12 +1540,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>续写与原文衔接自然,词汇灵活。</t>
+          <t>续写与原文衔接自然，词汇灵活。</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>作文评分记录</t>
+          <t>学生作文评分表</t>
         </is>
       </c>
     </row>
@@ -1597,12 +1597,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>细节生动,结尾有力,略有小错。</t>
+          <t>细节生动，结尾有力，略有小错。</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>作文评分记录</t>
+          <t>学生作文评分表</t>
         </is>
       </c>
     </row>
@@ -1654,12 +1654,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>情节合理,语言流畅,书写工整。</t>
+          <t>情节合理，语言流畅，书写工整。</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>作文评分记录</t>
+          <t>学生作文评分表</t>
         </is>
       </c>
     </row>
@@ -1711,12 +1711,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>细节生动,结尾有力,略有小错。</t>
+          <t>细节生动，结尾有力，略有小错。</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>作文评分记录</t>
+          <t>学生作文评分表</t>
         </is>
       </c>
     </row>
@@ -1768,12 +1768,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>主题明确,逻辑清晰,书写再工整些更佳。</t>
+          <t>主题明确，逻辑清晰，书写再工整些更佳。</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>作文评分记录</t>
+          <t>学生作文评分表</t>
         </is>
       </c>
     </row>
@@ -1825,12 +1825,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>偏离原文少许,但表达尚清楚。</t>
+          <t>偏离原文少许，但表达尚清楚。</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>作文评分记录</t>
+          <t>学生作文评分表</t>
         </is>
       </c>
     </row>
@@ -1882,12 +1882,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>主题明确,逻辑清晰,书写再工整些更佳。</t>
+          <t>主题明确，逻辑清晰，书写再工整些更佳。</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>作文评分记录</t>
+          <t>学生作文评分表</t>
         </is>
       </c>
     </row>
@@ -1939,12 +1939,12 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>故事完整,结构紧凑,表达有亮点。</t>
+          <t>故事完整，结构紧凑，表达有亮点。</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>作文评分记录</t>
+          <t>学生作文评分表</t>
         </is>
       </c>
     </row>
@@ -1996,12 +1996,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>故事完整,结构紧凑,表达有亮点。</t>
+          <t>故事完整，结构紧凑，表达有亮点。</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>作文评分记录</t>
+          <t>学生作文评分表</t>
         </is>
       </c>
     </row>
@@ -2053,12 +2053,12 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>句式较单一,字数刚好,书写可提高。</t>
+          <t>句式较单一，字数刚好，书写可提高。</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>作文评分记录</t>
+          <t>学生作文评分表</t>
         </is>
       </c>
     </row>
@@ -2110,12 +2110,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>情节略显突兀,语言可读性较好。</t>
+          <t>情节略显突兀，语言可读性较好。</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>作文评分记录</t>
+          <t>学生作文评分表</t>
         </is>
       </c>
     </row>
@@ -2167,12 +2167,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>细节生动,结尾有力,略有小错。</t>
+          <t>细节生动，结尾有力，略有小错。</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>作文评分记录</t>
+          <t>学生作文评分表</t>
         </is>
       </c>
     </row>
@@ -2224,12 +2224,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>内容基本相关,结构需更紧凑。</t>
+          <t>内容基本相关，结构需更紧凑。</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>作文评分记录</t>
+          <t>学生作文评分表</t>
         </is>
       </c>
     </row>
@@ -2281,12 +2281,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>句式较单一,字数刚好,书写可提高。</t>
+          <t>句式较单一，字数刚好，书写可提高。</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>作文评分记录</t>
+          <t>学生作文评分表</t>
         </is>
       </c>
     </row>
